--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122633373</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,345 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123339693</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 3075, Släthultagöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>576326</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6377990</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123339675</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 3075, Släthultagöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>576299</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6377945</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123339666</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 3075, Släthultagöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576299</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6377945</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339693</v>
+        <v>123339675</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +804,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576326</v>
+        <v>576299</v>
       </c>
       <c r="R3" t="n">
-        <v>6377990</v>
+        <v>6377945</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +888,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123339675</v>
+        <v>123339666</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +918,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1017,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339666</v>
+        <v>123339693</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,39 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576299</v>
+        <v>576326</v>
       </c>
       <c r="R5" t="n">
-        <v>6377945</v>
+        <v>6377990</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339675</v>
+        <v>123339666</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,37 +804,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123339666</v>
+        <v>123339675</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,37 +918,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         <v>123339693</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339666</v>
+        <v>123339693</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,39 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576299</v>
+        <v>576326</v>
       </c>
       <c r="R3" t="n">
-        <v>6377945</v>
+        <v>6377990</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339693</v>
+        <v>123339666</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1029,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576326</v>
+        <v>576299</v>
       </c>
       <c r="R5" t="n">
-        <v>6377990</v>
+        <v>6377945</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339666</v>
+        <v>123339675</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>57857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,37 +804,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -909,7 +909,7 @@
         <v>123339693</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339675</v>
+        <v>123339666</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1029,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339675</v>
+        <v>123339666</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,37 +804,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -909,7 +909,7 @@
         <v>123339693</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339666</v>
+        <v>123339675</v>
       </c>
       <c r="B5" t="n">
-        <v>57640</v>
+        <v>57860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1029,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123339666</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>123339693</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>123339675</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123339693</v>
+        <v>123339675</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,35 +918,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576326</v>
+        <v>576299</v>
       </c>
       <c r="R4" t="n">
-        <v>6377990</v>
+        <v>6377945</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1002,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339675</v>
+        <v>123339693</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,39 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576299</v>
+        <v>576326</v>
       </c>
       <c r="R5" t="n">
-        <v>6377945</v>
+        <v>6377990</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339666</v>
+        <v>123339675</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,37 +804,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123339675</v>
+        <v>123339693</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,39 +918,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576299</v>
+        <v>576326</v>
       </c>
       <c r="R4" t="n">
-        <v>6377945</v>
+        <v>6377990</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339693</v>
+        <v>123339666</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1029,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576326</v>
+        <v>576299</v>
       </c>
       <c r="R5" t="n">
-        <v>6377990</v>
+        <v>6377945</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339675</v>
+        <v>123339693</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,39 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576299</v>
+        <v>576326</v>
       </c>
       <c r="R3" t="n">
-        <v>6377945</v>
+        <v>6377990</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123339693</v>
+        <v>123339666</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,35 +915,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576326</v>
+        <v>576299</v>
       </c>
       <c r="R4" t="n">
-        <v>6377990</v>
+        <v>6377945</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339666</v>
+        <v>123339675</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1029,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>122633373</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -792,47 +787,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123339693</v>
+        <v>123339675</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576326</v>
+        <v>576299</v>
       </c>
       <c r="R3" t="n">
-        <v>6377990</v>
+        <v>6377945</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123339666</v>
+        <v>123339628</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,14 +926,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576299</v>
+        <v>576230</v>
       </c>
       <c r="R4" t="n">
-        <v>6377945</v>
+        <v>6377875</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,49 +1005,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123339675</v>
+        <v>123339666</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1128,6 +1111,324 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123339642</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 3075, Släthultagöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576263</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6377879</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123339693</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 3075, Släthultagöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576326</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6377990</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123339728</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 3075, Släthultagöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576257</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6377887</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3075-2025 artfynd.xlsx
+++ b/artfynd/A 3075-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122633373</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123339675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123339628</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123339666</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123339642</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123339693</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,8 +1464,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123339728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>